--- a/output/北塩原村_村HP掲載施策の棚卸し.xlsx
+++ b/output/北塩原村_村HP掲載施策の棚卸し.xlsx
@@ -2854,12 +2854,12 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>北塩原村障がい者活躍推進計画（障害者雇用促進法。第2期は令和7年度〜令和11年度）と北塩原村地域公共交通計画（令和7年度〜令和11年度）を関連計画として挙げる。いずれも本計画と期間が重なる</t>
+          <t>北塩原村障がい者活躍推進計画（障害者雇用促進法。第2期は令和7年度〜令和11年度）、北塩原村地域公共交通計画（令和7年度〜令和11年度）及び第10期北塩原村高齢者福祉計画・介護保険事業計画（令和9年度〜令和11年度）を関連計画として挙げる。高齢者福祉計画・介護保険事業計画は計画期間が本計画と完全に一致し、65歳到達・共生型サービス・適用除外・成年後見で数を揃える必要があるが、表に挙がっていなかった（令和8年10月10日に追加）</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>告示 第三の一の7。村ホームページ／アンケート調査（資料3）</t>
+          <t>告示 第三の一の7。村ホームページ／アンケート調査（資料3）／第10期介護保険事業計画の素案</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
@@ -3166,7 +3166,7 @@
       <c r="F6" s="6" t="inlineStr">
         <is>
           <t>また、本村には、本計画と計画期間が重なる次の計画があります。いずれも障がいのある方の生活に直に関わるため、本計画の推進にあたって整合を図ります。
-［表］計画 ／ 計画期間 ／ 本計画との関わり（2行）</t>
+［表］計画 ／ 計画期間 ／ 本計画との関わり（3行）</t>
         </is>
       </c>
     </row>

--- a/output/北塩原村_村HP掲載施策の棚卸し.xlsx
+++ b/output/北塩原村_村HP掲載施策の棚卸し.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>分野13件／手話の施策群5件（評価指標案9件）／情報保障・合理的配慮5件／移動・冬季2件／就労・社会参加4件／正本への反映7件（うち反映済み5件）／村への照会10件（M-59〜M-68）</t>
+          <t>分野13件／手話の施策群5件（評価指標案9件）／情報保障・合理的配慮5件／移動・冬季2件／就労・社会参加4件／正本への反映7件（うち反映済み5件）／村への照会10件（Ｍ-59〜Ｍ-68）</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -721,14 +721,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>この棚卸しで生じた村への照会（M-59〜M-68）</t>
+          <t>この棚卸しで生じた村への照会（Ｍ-59〜M-68）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>既存の照会はM-58まで。いずれも既存施策の実績を尋ねるものであり、村が手元で答えられるものが多い。</t>
+          <t>既存の照会はＭ-58まで。いずれも既存施策の実績を尋ねるものであり、村が手元で答えられるものが多い。</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>M-59</t>
+          <t>Ｍ-59</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -789,7 +789,7 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>M-60</t>
+          <t>Ｍ-60</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -816,7 +816,7 @@
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>M-61</t>
+          <t>Ｍ-61</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -843,7 +843,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>M-62</t>
+          <t>Ｍ-62</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -870,7 +870,7 @@
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>M-63</t>
+          <t>Ｍ-63</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -897,7 +897,7 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>M-64</t>
+          <t>Ｍ-64</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>第5章7（4）の村単独事業の記述を数値で裏づける。通院の負担は移動支援の論点（M-45・M-46）にもつながる</t>
+          <t>第5章7（4）の村単独事業の記述を数値で裏づける。通院の負担は移動支援の論点（Ｍ-45・Ｍ-46）にもつながる</t>
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>M-65</t>
+          <t>Ｍ-65</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>対象に含まれることが分かったため、次は実績である。M-55と同じ便で尋ねる</t>
+          <t>対象に含まれることが分かったため、次は実績である。Ｍ-55と同じ便で尋ねる</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
@@ -951,7 +951,7 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>M-66</t>
+          <t>Ｍ-66</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -978,7 +978,7 @@
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>M-67</t>
+          <t>Ｍ-67</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -1005,7 +1005,7 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>M-68</t>
+          <t>Ｍ-68</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>M-62</t>
+          <t>Ｍ-62</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>M-62</t>
+          <t>Ｍ-62</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>M-61</t>
+          <t>Ｍ-61</t>
         </is>
       </c>
     </row>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>M-63</t>
+          <t>Ｍ-63</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>M-64</t>
+          <t>Ｍ-64</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>M-49</t>
+          <t>Ｍ-49</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>M-67</t>
+          <t>Ｍ-67</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>M-68</t>
+          <t>Ｍ-68</t>
         </is>
       </c>
     </row>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>M-66</t>
+          <t>Ｍ-66</t>
         </is>
       </c>
     </row>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>照会M-64の回答後</t>
+          <t>照会Ｍ-64の回答後</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">

--- a/output/北塩原村_村HP掲載施策の棚卸し.xlsx
+++ b/output/北塩原村_村HP掲載施策の棚卸し.xlsx
@@ -848,12 +848,12 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>ヘルプマーク・ヘルプカード・耳マークの配布実績</t>
+          <t>ヘルプマーク・ヘルプカード・耳マーク・ほじょ犬マークの配布実績</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>年度別の配布数と、ヘルプカードの記載項目。救急時の様式（緊急連絡カード）との使い分けの整理</t>
+          <t>年度別の配布数と、ヘルプカードの記載項目。救急時の様式（緊急連絡カード）との使い分けの整理。ほじょ犬マークは第4次北塩原村障がい者計画がヘルプマーク・耳マークと並べて周知の対象に掲げており、村ホームページの棚卸しでは現れなかったため、現在も周知・配布をしておられるかをあわせて確認する</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>物品等の調達方針と実績</t>
+          <t>物品等の調達方針と令和6年度以降の実績</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>令和8年9月に更新された調達方針の内容、年度別の調達件数・金額・対象施設</t>
+          <t>令和8年9月に更新された調達方針の内容、令和6年度以降の年度別の調達件数・金額・対象施設。令和5年度までの実績は第4次北塩原村障がい者計画が「現在まで、北塩原村役場において、障がい者就労施設等からの物品調達の実績はありませんでした」と記しており0件であるため、重ねてお尋ねしない</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>なお、施策体系に現れていないことと、施策がないことは別です。本村は令和７年４月に「北塩原村手話言語条例」を制定し、公式動画による手話の紹介、指文字の紹介及び手話出前講座を行っているほか、ヘルプマーク、ヘルプカード、耳マーク及び電話お願い手帳の周知と配布を行っています。基本施策の整理にあたっては、これらの既に動いている取組みをどの施策の下に置くかという形で検討します。</t>
+          <t>なお、施策体系に現れていないことと、施策がないことは別です。本村は令和７年４月に「北塩原村手話言語条例」を制定し、公式動画による手話の紹介、指文字の紹介及び手話出前講座を行っているほか、ヘルプマーク、ヘルプカード、耳マーク、ほじょ犬マーク及び電話お願い手帳の周知と配布を行っています（ほじょ犬マークは第４次北塩原村障がい者計画が周知の対象として掲げているものです）。基本施策の整理にあたっては、これらの既に動いている取組みをどの施策の下に置くかという形で検討します。</t>
         </is>
       </c>
     </row>
